--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站沪南路高科西路 ETA 42分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±14分钟</t>
+          <t>07:19采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -880,22 +880,26 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -991,22 +999,26 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1058,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1175,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1286,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1324,19 +1340,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±5分钟</t>
+          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1351,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1380,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1400,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1443,19 +1459,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数161分钟估算，约±5分钟</t>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1470,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1499,32 +1515,1206 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>176分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>179分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数174分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>153分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>3/8</t>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>175分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数175分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>08:20采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1170,7 +1186,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1191,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1340,19 +1356,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1367,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1459,19 +1475,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1486,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1594,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1605,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±15分钟</t>
+          <t>08:20采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2024,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2046,24 +2062,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±12分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2073,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,7 +2113,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2122,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2165,24 +2181,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>179分钟</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数174分钟，约±10分钟</t>
+          <t>08:20采样：该车到重点站锦绣路花木路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2192,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2241,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>179.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2373,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2395,24 +2411,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2422,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2451,7 +2467,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2471,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2514,19 +2530,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>185分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数175分钟估算，约±12分钟</t>
+          <t>08:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2541,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2570,7 +2586,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2590,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2633,24 +2649,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2660,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2689,32 +2705,1571 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>172分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数150分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>163分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站博兴路兰城路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站川周公路康沈路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>3/18</t>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,27 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:01采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -907,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +927,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -994,29 +990,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1046,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1075,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1109,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1240,27 +1236,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1292,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1351,29 +1355,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1407,12 +1411,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1422,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1475,26 +1479,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1708,29 +1708,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路长柳路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1832,26 +1832,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>180分钟</t>
+          <t>178分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1859,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1888,7 +1884,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1908,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>178.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1941,12 +1937,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1974,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,10 +1978,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2003,7 +2015,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2062,24 +2074,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±8分钟</t>
+          <t>09:20采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2150,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2181,24 +2193,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站锦绣路花木路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+          <t>09:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2269,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2411,24 +2423,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±7分钟</t>
+          <t>09:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2438,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2530,24 +2542,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185分钟</t>
+          <t>192分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±12分钟</t>
+          <t>09:20采样：该车到重点站锦绣路花木路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2557,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,7 +2593,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2606,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2649,24 +2661,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
+          <t>09:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2676,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2737,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2768,24 +2780,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数150分钟，约±5分钟</t>
+          <t>09:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2795,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2856,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2887,19 +2899,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>09:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2914,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3006,24 +3018,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
+          <t>09:01采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3033,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3125,19 +3137,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站博兴路兰城路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>09:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3152,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3201,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3244,19 +3256,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+          <t>09:11采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3271,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3332,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3363,19 +3375,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站川周公路康沈路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>09:20采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3390,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3593,19 +3605,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+          <t>09:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3620,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3649,7 +3661,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3669,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3712,19 +3724,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+          <t>09:20采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3739,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3768,7 +3780,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3788,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3831,19 +3843,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+          <t>09:20采样：该车到重点站沪南路华夏西路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3858,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,7 +3899,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3907,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3942,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3950,24 +3962,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±11分钟</t>
+          <t>09:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3977,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3991,7 +4003,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4001,12 +4013,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4026,12 +4038,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4069,24 +4081,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+          <t>09:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4096,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4125,7 +4137,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4150,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4158,24 +4170,24 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4188,24 +4200,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±10分钟</t>
+          <t>09:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4215,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4229,7 +4241,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4239,37 +4251,854 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>122分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>140.5</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,12 +1530,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1594,24 +1598,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1713,24 +1717,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1827,27 +1831,31 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>178分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1855,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1887,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1894,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq60，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1970,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2069,24 +2077,24 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,12 +2133,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2140,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2196,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2205,12 +2213,12 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2220,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2252,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2259,22 +2267,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2310,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2335,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,10 +2351,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2364,7 +2388,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2423,26 +2447,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:50采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2450,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,7 +2499,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2489,22 +2509,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2542,26 +2562,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>192分钟</t>
+          <t>189分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站锦绣路花木路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2569,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2614,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2608,22 +2624,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2656,24 +2672,24 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2688,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2728,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2727,22 +2743,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2780,26 +2796,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2807,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2843,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2846,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2906,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2926,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,12 +2962,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2965,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3018,26 +3030,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:01采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3074,7 +3082,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3094,7 +3102,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3137,26 +3145,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,7 +3197,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3213,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3256,19 +3260,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:11采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站五莲路兰城路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3375,19 +3379,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3605,19 +3609,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3740,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3843,19 +3847,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站沪南路华夏西路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3923,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3966,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3974,12 +3978,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
+          <t>10:20采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4081,24 +4085,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±9分钟</t>
+          <t>10:20采样：该车到重点站金杨路金口路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4108,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,7 +4161,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4200,24 +4204,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±13分钟</t>
+          <t>10:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4251,7 +4255,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
@@ -4276,12 +4280,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4324,14 +4328,14 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4549,24 +4553,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±14分钟</t>
+          <t>10:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4600,12 +4604,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4625,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4783,19 +4787,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4839,7 +4843,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4859,7 +4863,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4902,22 +4906,26 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4969,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5017,19 +5025,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5073,32 +5081,984 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站博兴路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站川周公路康沈路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,22 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3140,27 +3140,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 9分钟</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,12 +3196,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3207,22 +3211,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3255,12 +3259,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3272,12 +3276,12 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站五莲路兰城路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3315,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3341,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3374,29 +3378,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3406,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,12 +3434,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3445,22 +3449,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3493,27 +3497,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3521,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3553,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3565,13 +3573,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3633,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>10:51采样：该车到重点站东葛路东靖路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数3分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3636,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3690,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3728,26 +3740,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3755,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,7 +3792,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3794,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3850,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3852,14 +3860,14 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3874,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,12 +3906,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3913,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3969,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3971,19 +3979,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3993,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,12 +4025,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4042,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4090,19 +4098,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金杨路金口路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4112,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,12 +4144,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4161,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4204,19 +4212,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>11:01采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4231,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4278,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4280,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4328,14 +4336,14 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4350,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4382,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4389,17 +4397,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4432,12 +4440,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4465,18 +4473,30 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4548,29 +4568,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4580,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,12 +4624,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4629,12 +4649,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4672,19 +4692,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 32分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
@@ -4695,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4739,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4787,19 +4807,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站康沈路秀沿路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4814,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,17 +4873,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4906,19 +4926,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4933,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5025,24 +5045,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5052,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5144,19 +5164,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站博兴路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>11:01采样：该车到重点站沪南路北中路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5171,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5263,7 +5283,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5275,7 +5295,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站川周公路康沈路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -5290,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5382,19 +5402,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -5409,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5501,24 +5521,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>11:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5528,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,12 +5572,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5577,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5620,19 +5640,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5647,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5676,7 +5696,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5696,12 +5716,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5739,19 +5759,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5766,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5795,7 +5815,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5815,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5858,24 +5878,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5885,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5914,7 +5934,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5934,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5977,24 +5997,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6004,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,32 +6053,1099 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>1/28</t>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,18 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2152,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2158,12 +2162,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,18 +2402,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2519,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2634,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,12 +2761,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2987,12 +2995,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3102,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3459,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4453,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4473,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4573,12 +4581,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4600,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4649,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4687,27 +4695,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4715,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4751,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4764,12 +4776,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4802,29 +4814,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站康沈路秀沿路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4834,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,12 +4870,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4883,12 +4895,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4921,29 +4933,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4953,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,12 +4989,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5002,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5040,29 +5052,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5072,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5108,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5121,12 +5133,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5164,26 +5176,22 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:01采样：该车到重点站沪南路北中路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:01采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5191,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,7 +5228,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5240,12 +5248,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5278,24 +5286,24 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -5310,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,12 +5342,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5349,7 +5357,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5359,12 +5367,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5397,29 +5405,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5429,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5461,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5478,12 +5486,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5521,26 +5529,22 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5548,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,7 +5581,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5597,12 +5601,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5635,29 +5639,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5667,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5695,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5716,12 +5720,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5759,19 +5763,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5786,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,12 +5839,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5878,24 +5882,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±6分钟</t>
+          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5905,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5997,24 +6001,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±9分钟</t>
+          <t>12:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6024,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6077,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6116,19 +6120,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,12 +6196,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6235,19 +6239,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6262,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,12 +6315,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6354,19 +6358,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6381,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6434,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6473,24 +6477,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6529,7 +6533,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6549,12 +6553,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6673,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6727,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6738,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,7 +6771,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6792,7 +6796,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6945,19 +6949,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±13分钟</t>
+          <t>12:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6972,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,7 +7005,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7021,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,12 +7144,484 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,22 +2751,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3810,22 +3810,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5476,22 +5476,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5524,27 +5524,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5552,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,12 +5580,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5601,12 +5605,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5644,24 +5648,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5671,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,22 +5714,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5762,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5775,12 +5779,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站五莲路兰城路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5790,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,12 +5818,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5829,22 +5833,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5877,12 +5881,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5894,7 +5898,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5909,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,12 +5937,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5996,12 +6000,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6013,12 +6017,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6028,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,12 +6056,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6082,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6115,24 +6119,24 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6147,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,12 +6175,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6186,22 +6190,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6234,24 +6238,24 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6266,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,12 +6294,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6305,22 +6309,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6353,29 +6357,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6385,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6409,12 +6413,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6434,12 +6438,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6472,29 +6476,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6504,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,12 +6532,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6543,22 +6547,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6715,24 +6719,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±15分钟</t>
+          <t>13:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6742,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6766,7 +6770,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
@@ -6791,7 +6795,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6911,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6949,19 +6953,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±13分钟</t>
+          <t>13:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6976,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7029,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7068,26 +7072,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 88分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7187,19 +7187,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>13:01采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7306,19 +7306,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>13:20采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7425,22 +7425,26 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>13:20采样：该车到重点站金杨路金业路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7448,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7492,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7540,19 +7544,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±7分钟</t>
+          <t>13:20采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7567,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7596,32 +7600,857 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>13:20采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>1/29</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,14 +1426,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>152.0</t>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2038,17 +2038,13 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2162,7 +2158,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2232,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2281,7 +2277,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2347,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2532,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3825,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3939,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4048,14 +4044,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4405,22 +4401,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4723,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4766,14 +4762,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>152.0</t>
@@ -4781,7 +4777,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4842,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4885,22 +4881,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,17 +5005,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5134,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5367,7 +5363,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5437,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5486,7 +5482,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5610,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5843,12 +5839,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5963,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6082,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6200,12 +6196,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6314,17 +6310,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6439,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6493,12 +6489,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6508,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6562,7 +6558,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6595,29 +6591,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±13分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6627,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,12 +6647,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6676,12 +6672,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6714,29 +6710,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6746,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6766,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6785,22 +6781,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6948,29 +6944,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6980,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,12 +7000,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7019,22 +7015,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7067,12 +7063,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -7084,10 +7080,14 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 88分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7177,36 +7177,32 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13:01采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>10:01</t>
@@ -7214,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,10 +7218,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq19（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7238,17 +7246,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7258,17 +7266,13 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7306,26 +7310,22 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:01采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,17 +7357,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7377,17 +7377,13 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7425,19 +7421,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路金业路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±5分钟</t>
+          <t>14:01采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7452,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7501,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7544,7 +7540,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7556,12 +7552,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±7分钟</t>
+          <t>14:01采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7571,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7663,19 +7659,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>14:01采样：该车到重点站白桦路明月路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7690,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7739,12 +7735,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7901,19 +7897,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±7分钟</t>
+          <t>14:01采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7928,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7957,7 +7953,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7977,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8020,22 +8016,26 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>14:01采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8087,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8135,19 +8135,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>14:01采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8450,7 +8450,471 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>136.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,18 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2162,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2408,7 +2412,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,7 +2761,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4416,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4891,7 +4895,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4961,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5010,7 +5014,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5134,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,22 +5238,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5363,12 +5367,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5482,12 +5486,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5729,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5839,7 +5843,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5963,7 +5967,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6196,12 +6200,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6320,7 +6324,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6553,12 +6557,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6796,7 +6800,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6949,24 +6953,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6976,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,7 +7029,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7068,12 +7072,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7095,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,7 +7148,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7210,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,27 +7309,31 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:01采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7333,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,33 +7365,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7421,19 +7433,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7448,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7509,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7540,24 +7552,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±6分钟</t>
+          <t>14:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7567,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,7 +7628,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7659,19 +7671,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站白桦路明月路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站沪南路北中路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7686,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,7 +7747,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7859,7 +7871,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7897,19 +7909,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±7分钟</t>
+          <t>14:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7924,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7985,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8028,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -8043,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8109,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8135,24 +8147,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,12 +8223,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8254,19 +8266,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8281,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8310,7 +8322,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8330,12 +8342,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8450,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8680,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8794,7 +8806,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8860,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8914,7 +8926,245 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,22 +3338,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5714,22 +5714,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6790,17 +6790,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7072,24 +7072,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7314,24 +7314,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7428,24 +7428,24 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7547,29 +7547,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7666,24 +7666,24 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>118分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路北中路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,22 +7856,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7904,29 +7904,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8033,21 +8033,17 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8055,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,12 +8075,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8104,12 +8100,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8147,26 +8143,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8174,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,12 +8190,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8223,12 +8215,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8258,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -8278,7 +8270,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>15:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8293,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8347,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8462,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8500,22 +8492,26 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8523,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8547,17 +8543,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8567,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8615,22 +8611,26 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站沪南路高科西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,17 +8662,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8730,19 +8730,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8849,22 +8849,26 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站川周公路康沈路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8900,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8916,17 +8920,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9040,12 +9044,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9053,24 +9057,24 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9083,34 +9087,30 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,37 +9134,501 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>144.3</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>17/29</t>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>154分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,22 +2402,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,14 +5123,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>147.5</t>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5952,22 +5952,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6666,14 +6666,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7618,22 +7618,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8023,27 +8023,31 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8051,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,12 +8079,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8100,12 +8104,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8138,27 +8142,31 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8166,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,12 +8198,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8215,12 +8223,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8253,29 +8261,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8285,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,12 +8317,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8334,12 +8342,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8372,27 +8380,31 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8400,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,17 +8436,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8444,17 +8456,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8487,29 +8499,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8519,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,12 +8555,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8568,7 +8580,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8606,29 +8618,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站沪南路高科西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8638,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,12 +8674,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8687,12 +8699,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8730,24 +8742,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
+          <t>16:20采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8757,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8806,12 +8818,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8849,24 +8861,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站川周公路康沈路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
+          <t>16:20采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8876,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,7 +8912,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
@@ -8925,12 +8937,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8980,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -8980,12 +8992,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±8分钟</t>
+          <t>16:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8995,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,12 +9031,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9110,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9317,24 +9329,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+          <t>16:20采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9344,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9373,7 +9385,7 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9393,7 +9405,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9436,24 +9448,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±12分钟</t>
+          <t>16:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9463,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,12 +9499,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9512,12 +9524,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9525,24 +9537,24 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9555,30 +9567,34 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9592,43 +9608,971 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr"/>
-      <c r="AC77" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数144分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>116分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>138.3</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,14 +2152,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4766,22 +4766,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5595,14 +5595,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6671,17 +6671,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6900,17 +6900,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,22 +7138,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7499,14 +7499,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8385,24 +8385,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,22 +8451,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8504,24 +8504,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8737,29 +8737,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8856,29 +8856,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8927,22 +8927,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8975,29 +8975,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9089,12 +9089,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,10 +9130,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9151,7 +9167,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9291,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9329,26 +9345,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 53分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9356,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,17 +9392,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9400,12 +9412,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9448,24 +9460,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±6分钟</t>
+          <t>17:20采样：该车到重点站云山路碧云路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9475,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9524,12 +9536,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9567,24 +9579,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±13分钟</t>
+          <t>17:20采样：该车到重点站沪南路北中路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9594,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9643,12 +9655,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9797,24 +9809,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数144分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9824,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9873,12 +9885,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9916,19 +9928,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>116分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9943,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9992,12 +10004,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10035,22 +10047,26 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站迎春路长柳路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10058,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,17 +10098,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10102,17 +10118,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10227,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10342,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10380,22 +10396,26 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10403,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10447,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10447,17 +10467,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10465,24 +10485,24 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10495,30 +10515,34 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,37 +10566,969 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金杨路金业路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>147.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金杨路金业路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站川周公路康沈路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X85" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>147.5</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>24/30</t>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>144.3</t>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,14 +2985,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,22 +3338,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5238,14 +5238,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>144.3</t>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5600,17 +5600,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6071,14 +6071,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7742,17 +7742,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7790,24 +7790,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±12分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8094,22 +8094,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8694,17 +8694,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8861,24 +8861,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9292,14 +9292,14 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>144.3</t>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9340,27 +9340,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 53分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9368,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,37 +9396,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9459,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9465,14 +9469,14 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站云山路碧云路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9487,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9511,12 +9515,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9541,7 +9545,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9574,29 +9578,29 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路北中路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9606,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9630,12 +9634,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9645,22 +9649,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9775,7 @@
       <c r="AB78" s="2" t="inlineStr"/>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9809,26 +9813,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:19</t>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9928,26 +9928,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9955,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9984,7 +9980,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -10004,12 +10000,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10047,19 +10043,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站迎春路长柳路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10074,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10123,12 +10119,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,7 +10239,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10358,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10396,19 +10392,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10423,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10472,12 +10468,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10515,19 +10511,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10542,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10591,12 +10587,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10634,19 +10630,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路金业路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10661,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10710,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10753,19 +10749,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路金业路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10780,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10829,12 +10825,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10877,14 +10873,14 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站川周公路康沈路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站锦绣路花木路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10899,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10948,12 +10944,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10991,22 +10987,26 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11058,17 +11058,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11106,22 +11106,26 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11129,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11153,17 +11157,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11173,17 +11177,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11221,22 +11225,26 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11244,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11268,17 +11276,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11288,17 +11296,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11336,22 +11344,26 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11359,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11383,17 +11395,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11403,17 +11415,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11421,24 +11433,24 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11451,30 +11463,34 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11498,37 +11514,838 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="X94" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>149.3</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>25/30</t>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,22 +4167,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5714,22 +5714,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6428,22 +6428,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,22 +7856,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9297,17 +9297,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9530,22 +9530,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9654,17 +9654,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9808,27 +9808,31 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:19</t>
@@ -9836,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,12 +9864,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9875,7 +9879,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9885,12 +9889,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9923,27 +9927,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9951,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9975,12 +9983,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -10000,7 +10008,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10038,29 +10046,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10070,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10094,12 +10102,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10109,22 +10117,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10157,27 +10165,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10185,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10209,37 +10221,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10277,19 +10289,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:10采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
@@ -10300,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10324,37 +10336,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10387,12 +10399,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -10404,12 +10416,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10419,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,12 +10455,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10458,7 +10470,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10506,12 +10518,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -10523,12 +10535,12 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10538,7 +10550,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,12 +10574,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10592,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10630,26 +10642,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:10采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10657,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10686,7 +10694,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10696,22 +10704,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10749,19 +10757,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站周东路川周公路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10776,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10825,12 +10833,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10868,26 +10876,22 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站锦绣路花木路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10895,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10919,12 +10923,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10944,12 +10948,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10987,19 +10991,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11014,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11063,7 +11067,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11106,19 +11110,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11133,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11182,12 +11186,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11225,19 +11229,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站金杨路金口路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11252,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11301,12 +11305,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11344,19 +11348,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>19:10采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11371,7 +11375,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11420,12 +11424,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -11463,19 +11467,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11490,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11539,12 +11543,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11605,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11720,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11835,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11927,22 +11931,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11950,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11982,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11994,17 +12002,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12153,22 +12161,26 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12176,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12200,17 +12212,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12220,17 +12232,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12268,22 +12280,26 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站博兴路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12291,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12315,37 +12331,858 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>9/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站康沈路秀康路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>141.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>159分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数140分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>26/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z104" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>17/31</t>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>15/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>12/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,22 +2517,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5595,22 +5595,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5952,22 +5952,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10757,26 +10757,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站周东路川周公路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10784,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10813,7 +10809,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10833,12 +10829,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10867,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -10881,17 +10877,21 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -11003,14 +11003,10 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11018,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11042,12 +11038,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11057,22 +11053,22 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11110,26 +11106,22 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11137,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11161,12 +11153,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11186,7 +11178,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11229,19 +11221,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路金口路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11256,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11305,12 +11297,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11429,7 +11421,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11467,19 +11459,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11494,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11543,12 +11535,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11724,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11839,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11931,7 +11923,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -11943,7 +11935,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11958,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12073,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12161,19 +12153,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
+          <t>19:31采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -12188,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12237,12 +12229,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12353,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12391,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -12411,7 +12403,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -12426,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12480,7 +12472,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12510,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -12530,7 +12522,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站康沈路秀康路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
+          <t>19:31采样：该车到重点站康沈路秀康路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -12545,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12599,7 +12591,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12629,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -12649,7 +12641,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数140分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数140分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12664,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12779,7 +12771,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12894,7 +12886,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12948,7 +12940,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13001,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13063,7 +13055,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13071,24 +13063,24 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -13101,34 +13093,34 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13142,47 +13134,285 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>142.2</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>15/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
+      <c r="Z108" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA107" s="2" t="inlineStr">
+      <c r="AA108" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB107" s="2" t="inlineStr">
+      <c r="AB108" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
         </is>
       </c>
-      <c r="AC107" s="2" t="inlineStr">
-        <is>
-          <t>12/31</t>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC109"/>
+  <dimension ref="A1:AC111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,22 +2985,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6071,22 +6071,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6190,22 +6190,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8213,22 +8213,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8932,17 +8932,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10752,27 +10752,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10780,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10804,12 +10808,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10829,12 +10833,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10872,24 +10876,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10899,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10948,12 +10952,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10986,27 +10990,31 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11014,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11038,12 +11046,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11063,12 +11071,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11101,27 +11109,31 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11129,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11153,12 +11165,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11178,7 +11190,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11216,29 +11228,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11248,7 +11260,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11272,12 +11284,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11297,7 +11309,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11335,24 +11347,24 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:10采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11367,7 +11379,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11391,12 +11403,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11416,12 +11428,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11454,29 +11466,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11486,7 +11498,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11510,12 +11522,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11535,12 +11547,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11578,19 +11590,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
@@ -11601,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11625,17 +11637,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11645,17 +11657,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11782,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11803,27 +11815,31 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11831,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11855,37 +11871,37 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11923,19 +11939,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站东波路莱阳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11950,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11999,12 +12015,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>150.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12153,24 +12169,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±15分钟</t>
+          <t>20:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12180,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,7 +12220,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
@@ -12229,12 +12245,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12369,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -12391,19 +12407,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>20:10采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -12418,7 +12434,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12467,12 +12483,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12510,19 +12526,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站康沈路秀康路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
+          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -12537,7 +12553,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12586,12 +12602,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -12629,19 +12645,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数140分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12656,7 +12672,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12705,12 +12721,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12787,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12886,7 +12902,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12940,7 +12956,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13017,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13093,24 +13109,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>20:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13120,7 +13136,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13149,7 +13165,7 @@
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
@@ -13169,12 +13185,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -13182,24 +13198,24 @@
       <c r="A108" s="2" t="inlineStr"/>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -13212,34 +13228,34 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+          <t>20:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13253,7 +13269,7 @@
       <c r="T108" s="2" t="inlineStr"/>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
@@ -13268,7 +13284,7 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
@@ -13288,12 +13304,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -13301,7 +13317,7 @@
       <c r="A109" s="2" t="inlineStr"/>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -13311,7 +13327,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -13331,34 +13347,34 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>22:39</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>20:20采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13372,47 +13388,285 @@
       <c r="T109" s="2" t="inlineStr"/>
       <c r="U109" s="2" t="inlineStr">
         <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="V109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W109" s="2" t="inlineStr">
+      <c r="W110" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X109" s="2" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y109" s="2" t="inlineStr">
+      <c r="Y110" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z109" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA109" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB109" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="AC109" s="2" t="inlineStr">
-        <is>
-          <t>7/31</t>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>138.8</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>9/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB111" s="2" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6433,17 +6433,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11595,17 +11595,21 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11613,7 +11617,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11637,12 +11641,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11662,12 +11666,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11896,7 +11900,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11934,29 +11938,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站东波路莱阳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11966,7 +11970,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11990,12 +11994,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -12015,12 +12019,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -12053,27 +12057,31 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -12081,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12105,17 +12113,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12125,13 +12133,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB98" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12164,29 +12176,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12196,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12220,12 +12232,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12245,12 +12257,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12397,36 +12409,32 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:10采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12434,18 +12442,30 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
       <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12458,17 +12478,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12478,17 +12498,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12521,29 +12541,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12553,7 +12573,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12577,12 +12597,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12602,12 +12622,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -12640,24 +12660,24 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12672,7 +12692,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12696,12 +12716,12 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12721,7 +12741,7 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12787,7 +12807,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12841,7 +12861,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12869,12 +12889,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -12902,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12910,10 +12930,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q105" s="2" t="inlineStr"/>
-      <c r="R105" s="2" t="inlineStr"/>
-      <c r="S105" s="2" t="inlineStr"/>
-      <c r="T105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12931,7 +12967,7 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12956,7 +12992,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13053,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13071,7 +13107,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13104,29 +13140,29 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13136,7 +13172,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13160,12 +13196,12 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
@@ -13185,12 +13221,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -13228,19 +13264,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -13255,7 +13291,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13304,7 +13340,7 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
@@ -13347,24 +13383,24 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
+          <t>21:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -13374,7 +13410,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13423,12 +13459,12 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -13471,19 +13507,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>21:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -13493,7 +13529,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13517,12 +13553,12 @@
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
@@ -13542,12 +13578,12 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13585,24 +13621,24 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -13612,7 +13648,7 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
@@ -13641,7 +13677,7 @@
       </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y111" s="2" t="inlineStr">
@@ -13661,7 +13697,7 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">

--- a/data/export/2026-09-17-浦东35路.xlsx
+++ b/data/export/2026-09-17-浦东35路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5600,17 +5600,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13145,24 +13145,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -13269,19 +13269,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
@@ -13383,26 +13383,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -13410,7 +13406,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13439,7 +13435,7 @@
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
@@ -13459,7 +13455,7 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
@@ -13502,26 +13498,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>22:39</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 54分钟</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -13529,7 +13521,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13553,17 +13545,17 @@
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr">
@@ -13573,17 +13565,17 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13621,24 +13613,24 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±8分钟</t>
+          <t>21:51采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -13648,7 +13640,7 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
@@ -13697,7 +13689,7 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
